--- a/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_67610_completo.xlsx
+++ b/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_67610_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R882b9e7a6563452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R87d65b22873a4b15"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4263</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8024</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.0557</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.7177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.1072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.1305</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,13 +399,73 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     27.7419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.1418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     27.3460</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>13/08/2026</x:t>
+          <x:t>09/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -285,7 +480,307 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>12/08/2026</x:t>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8024</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4263</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8024</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.3460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -300,22 +795,52 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>11/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.9542</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/08/2026</x:t>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.1418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.5457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -330,22 +855,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7419</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
+          <x:t>14/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -360,202 +870,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7419</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1824</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1824</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.6858</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.0541</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.0541</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1824</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.8024</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.4263</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.9542</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1824</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.8024</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.9542</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
+          <x:t>13/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -570,127 +885,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.9542</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7419</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7419</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7419</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7419</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.1418</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7419</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.1418</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
+          <x:t>12/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -705,66 +900,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.3460</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.5663</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.3460</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.5457</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>11/07/2026</x:t>
         </x:is>
       </x:c>
@@ -804,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.2025</x:v>
+        <x:v>     30.6270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.0557</x:v>
+        <x:v>     30.6270</x:v>
       </x:c>
     </x:row>
     <x:row>
